--- a/Yoedu_Management_Test_Case.xlsx
+++ b/Yoedu_Management_Test_Case.xlsx
@@ -8,13 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Automate test\Test case\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7BE0D4EE-59F2-43CC-ABD9-919EBEE1F95F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB89A10C-8063-4280-8E42-ADC02E3D6A17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-90" yWindow="-90" windowWidth="19380" windowHeight="12180" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-90" yWindow="-90" windowWidth="19380" windowHeight="12180" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Phòng học" sheetId="1" r:id="rId1"/>
-    <sheet name="Học viên" sheetId="2" r:id="rId2"/>
+    <sheet name="Phòng học" sheetId="2" r:id="rId1"/>
+    <sheet name="Học viên" sheetId="1" r:id="rId2"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="389" uniqueCount="245">
   <si>
     <t>Test Case</t>
   </si>
@@ -53,14 +53,1256 @@
   </si>
   <si>
     <t>Notes</t>
+  </si>
+  <si>
+    <t>rooms</t>
+  </si>
+  <si>
+    <t>Verify UI of Classroom list page</t>
+  </si>
+  <si>
+    <t>Logged into YoEdu, on Rooms page</t>
+  </si>
+  <si>
+    <t>1. Observe the data table and pagination</t>
+  </si>
+  <si>
+    <t>All columns and pagination are displayed</t>
+  </si>
+  <si>
+    <t>Pass</t>
+  </si>
+  <si>
+    <t>Verify Pagination functionality</t>
+  </si>
+  <si>
+    <t>Verify Search by Room Code</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Verify "Add New Room" button </t>
+  </si>
+  <si>
+    <t>Verify changing Room Status</t>
+  </si>
+  <si>
+    <t>Verify Action menu (...)</t>
+  </si>
+  <si>
+    <t>Verify "Select All" checkbox</t>
+  </si>
+  <si>
+    <t>1. Click on page number '2' or the next arrow &gt; and &lt;</t>
+  </si>
+  <si>
+    <t>1. Click on "Tìm kiếm..." box
+2. Enter a valid code (e.g., PHONG_AUTO_2801)
+3. Press Enter / Wait</t>
+  </si>
+  <si>
+    <t>Table displays columns: Mã, Tên, Diễn giải, Trạng thái, Tác vụ. 
+Pagination shows pages (1, 2, 3...)</t>
+  </si>
+  <si>
+    <t>System navigates to page 2 and 
+loads the next set of rooms or load the previous set of rooms</t>
+  </si>
+  <si>
+    <t>Next pages load when click &gt; and previous pages load when click &lt;; 
+when click page numbers it loads the exact pages</t>
+  </si>
+  <si>
+    <t>The table reloads and displays only the room with the matching code</t>
+  </si>
+  <si>
+    <t>A modal or new page opens allowing user to input new room details</t>
+  </si>
+  <si>
+    <t>Toggle turns grey (inactive), system displays a success notification</t>
+  </si>
+  <si>
+    <t>A dropdown menu opens displaying actions (e.g., Edit, Delete)</t>
+  </si>
+  <si>
+    <t>All checkboxes for the rooms on the current page are ticked</t>
+  </si>
+  <si>
+    <t>1. Click the checkbox in the table header (next to "Mã")</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">1. Click the </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>...</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> icon under "Tác vụ" column for any room</t>
+    </r>
+  </si>
+  <si>
+    <t>1. Find a room with active status (blue toggle)
+2. Click the toggle switch</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">1. Click the </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> icon on the top right</t>
+    </r>
+  </si>
+  <si>
+    <t>Verify Search with leading and trailing spaces</t>
+  </si>
+  <si>
+    <t>Verify Search with special HTML/SQL characters</t>
+  </si>
+  <si>
+    <t>Verify checkbox state persistence across pages</t>
+  </si>
+  <si>
+    <t>Verify rapid clicking on Status toggle</t>
+  </si>
+  <si>
+    <t>Verify UI behavior when clicking outside the Action menu</t>
+  </si>
+  <si>
+    <t>Verify responsive UI on browser resize</t>
+  </si>
+  <si>
+    <t>1. Click on the Search box
+2. Enter a valid room code with extra spaces (e.g., " PHONG_AUTO_2801 ")
+3. Press Enter</t>
+  </si>
+  <si>
+    <t>System automatically trims the spaces and returns the correct room matching the code.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">1. Enter special characters in Search box (e.g., </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>' OR 1=1 --</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>&lt;script&gt;alert(1)&lt;/script&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <t>System handles the input securely, displays "No data found", and does not execute the script or crash.</t>
+  </si>
+  <si>
+    <t>1. Select the checkbox of the first room on Page 1
+2. Navigate to Page 2 using pagination
+3. Navigate back to Page 1</t>
+  </si>
+  <si>
+    <t>The checkbox for the selected room on Page 1 should still remain checked.</t>
+  </si>
+  <si>
+    <t>1. Find a room and rapidly click its Status toggle switch 4-5 times in a row</t>
+  </si>
+  <si>
+    <t>System processes the final state correctly without throwing multiple conflicting popup errors or crashing.</t>
+  </si>
+  <si>
+    <t>1. Click the ... icon to open the action dropdown
+2. Click anywhere else outside the dropdown menu</t>
+  </si>
+  <si>
+    <t>The dropdown menu should close immediately.</t>
+  </si>
+  <si>
+    <t>1. Restore down the browser window
+2. Resize the width to be very narrow (mobile/tablet view)</t>
+  </si>
+  <si>
+    <t>The data table should add a horizontal scrollbar or adjust columns to prevent data from overflowing or overlapping.</t>
+  </si>
+  <si>
+    <t>Verify hyperlink navigation for Room Code and Name</t>
+  </si>
+  <si>
+    <t>Verify Search with non-existent data</t>
+  </si>
+  <si>
+    <t>Verify UI response on individual Checkbox selection</t>
+  </si>
+  <si>
+    <t>1. Hover over and click the blue underlined text in the "Mã" (Code) 
+or "Tên" (Name) column (e.g., PHONG_AUTO_9499).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Click on the Search box.
+2. Enter a non-existent text string (e.g., XYZ_999_@#$).
+</t>
+  </si>
+  <si>
+    <t>1. Click the square checkbox on the left side of any 1 or 2 rooms in the list.</t>
+  </si>
+  <si>
+    <t>The checkboxes are ticked. The system may display bulk action buttons (e.g., Delete selected).</t>
+  </si>
+  <si>
+    <t>The data table displays a "No data found" message and the system does not crash.</t>
+  </si>
+  <si>
+    <t>System navigates to the corresponding "Room Details" page.</t>
+  </si>
+  <si>
+    <t>Verify clearing the Search input restores the full list</t>
+  </si>
+  <si>
+    <t>1. Search for a specific room (e.g., "Room DUP").
+2. Delete the text in the search box so it is empty.</t>
+  </si>
+  <si>
+    <t>The table reloads and displays the default full list of all rooms.</t>
+  </si>
+  <si>
+    <t>Verify Read-Only state of Room Details page</t>
+  </si>
+  <si>
+    <t>Verify Back button functionality</t>
+  </si>
+  <si>
+    <t>Verify Image rendering on Details page</t>
+  </si>
+  <si>
+    <t>1. Observe the "Hình ảnh" (Image) section at the bottom.</t>
+  </si>
+  <si>
+    <t>The uploaded image of the room should be displayed clearly.</t>
+  </si>
+  <si>
+    <r>
+      <t>1. Click the back arrow icon (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>&lt;-</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>) next to "Chi tiết".</t>
+    </r>
+  </si>
+  <si>
+    <t>System navigates back to the Classroom list page without data loss or errors.</t>
+  </si>
+  <si>
+    <t>1. Attempt to click and type into any input fields (Mã, Tên, Diễn giải, etc.).
+2. Attempt to open dropdowns (Cơ Sở, Trạng thái).</t>
+  </si>
+  <si>
+    <t>All fields and dropdowns are disabled/read-only. User cannot modify any data.</t>
+  </si>
+  <si>
+    <t>Verify successful Room Update with valid data</t>
+  </si>
+  <si>
+    <t>Verify Edit validation on required fields</t>
+  </si>
+  <si>
+    <t>Verify successful Room Deletion</t>
+  </si>
+  <si>
+    <t>Verify canceling Deletion</t>
+  </si>
+  <si>
+    <t>1. Click ... -&gt; Select Xóa (Delete).
+2. Click "Cancel" or "No" on the confirmation popup.</t>
+  </si>
+  <si>
+    <t>1. Click ... on a test room -&gt; Select Xóa (Delete).
+2. Confirm the deletion on the popup.</t>
+  </si>
+  <si>
+    <t>1. Click ... -&gt; Select Sửa (Edit).
+2. Delete the text in the "Tên" (Name) field to leave it blank.
+3. Click Save.</t>
+  </si>
+  <si>
+    <t>1. Click ... on a room -&gt; Select Sửa (Edit).
+2. Change the Room Name or Description.
+3. Click Save.</t>
+  </si>
+  <si>
+    <t>System displays success message. The table updates with the new information.</t>
+  </si>
+  <si>
+    <t>System prevents saving and shows an error: "Tên phòng là bắt buộc" (Name is required).</t>
+  </si>
+  <si>
+    <t>System shows success message. The room is removed from the data table.</t>
+  </si>
+  <si>
+    <t>The popup closes and the room remains untouched in the data table.</t>
+  </si>
+  <si>
+    <t>On "Tạo mới" page</t>
+  </si>
+  <si>
+    <t>Verify successful room creation with all valid data</t>
+  </si>
+  <si>
+    <t>Verify creation fails when required fields are blank</t>
+  </si>
+  <si>
+    <t>Verify successful creation with only required fields</t>
+  </si>
+  <si>
+    <t>1. Leave Mã*, Tên*, and Cơ Sở* empty.
+2. Click "LƯU".</t>
+  </si>
+  <si>
+    <t>1. Enter valid data in "Mã", "Tên".
+2. Select a valid "Cơ Sở".
+3. Enter valid "Số lượng học sinh" (e.g., 30).
+4. Upload a valid image.
+5. Click "LƯU" (Save).</t>
+  </si>
+  <si>
+    <t>1. Fill in ONLY Mã*, Tên*, and Cơ Sở*.
+2. Leave others blank or default.
+3. Click "LƯU".</t>
+  </si>
+  <si>
+    <t>System successfully creates the room with empty optional fields.</t>
+  </si>
+  <si>
+    <t>System prevents saving and displays error messages under each required field (e.g., "This field is required").</t>
+  </si>
+  <si>
+    <t>System saves data, redirects to list page, and shows a success message.</t>
+  </si>
+  <si>
+    <t>Verify "Số lượng học sinh" does not accept negative numbers</t>
+  </si>
+  <si>
+    <t>Verify "Số lượng học sinh" does not accept text/special characters</t>
+  </si>
+  <si>
+    <t>Verify Max Length validation for "Mã" and "Tên"</t>
+  </si>
+  <si>
+    <t>Verify Image upload with invalid file format</t>
+  </si>
+  <si>
+    <t>Verify Image Drag and Drop functionality</t>
+  </si>
+  <si>
+    <t>Verify "Back" navigation with unsaved data</t>
+  </si>
+  <si>
+    <t>Verify form submission using 'Enter' key</t>
+  </si>
+  <si>
+    <t>1. Fill all required fields.
+2. While the cursor is in a text box, press the Enter key on the keyboard.</t>
+  </si>
+  <si>
+    <t>1. Enter some text in "Tên" or "Mã".
+2. Do NOT click Save.
+3. Click the Back arrow (&lt;-) next to "Tạo mới".</t>
+  </si>
+  <si>
+    <t>The form submits successfully as if the "LƯU" button was clicked.</t>
+  </si>
+  <si>
+    <t>System should show a warning popup: "Unsaved changes will be lost. Do you want to leave?"</t>
+  </si>
+  <si>
+    <t>1. Type letters (e.g., abc) or special characters (e.g., @#$) into the field.</t>
+  </si>
+  <si>
+    <t>System shows validation error (e.g., "Must be greater than 0") and prevents saving.</t>
+  </si>
+  <si>
+    <t>Field should block text input automatically, OR system shows an error when clicking "LƯU".</t>
+  </si>
+  <si>
+    <t>System should prevent input beyond limit OR show a validation error message.</t>
+  </si>
+  <si>
+    <t>System prevents the upload and shows an error: "Invalid file format".</t>
+  </si>
+  <si>
+    <t>The image is uploaded successfully and a preview/filename is displayed.</t>
+  </si>
+  <si>
+    <t>1. Drag an image file from the computer desktop.
+2. Drop it into the dashed upload area.</t>
+  </si>
+  <si>
+    <t>1. Click "CHỌN HÌNH ẢNH".
+2. Select a non-image file (e.g., .pdf, .docx, .exe).</t>
+  </si>
+  <si>
+    <t>1. Enter a very long string (&gt; 255 characters) in "Mã" and "Tên".
+2. Click "LƯU".</t>
+  </si>
+  <si>
+    <t>1. Enter a negative number (e.g., -5) into "Số lượng học sinh".
+2. Click "LƯU".</t>
+  </si>
+  <si>
+    <t>Verify system handles oversized image uploads</t>
+  </si>
+  <si>
+    <t>1. Click "CHỌN HÌNH ẢNH".
+2. Select an extremely large image file (e.g., &gt; 10MB or 20MB).</t>
+  </si>
+  <si>
+    <t>System prevents upload and shows an error message (e.g., "File size exceeds limit"). It should not crash or hang.</t>
+  </si>
+  <si>
+    <t>Verify Delete confirmation popup UI</t>
+  </si>
+  <si>
+    <t>Verify "ĐÓNG" button cancels deletion</t>
+  </si>
+  <si>
+    <t>Verify Room Code is read-only during Edit</t>
+  </si>
+  <si>
+    <t>Verify Image rendering in Edit mode</t>
+  </si>
+  <si>
+    <t>Verify "Trạng thái" dropdown functionality</t>
+  </si>
+  <si>
+    <t>Verify clearing "Trạng thái" using the 'x' icon</t>
+  </si>
+  <si>
+    <t>On Edit Room page</t>
+  </si>
+  <si>
+    <t>On Rooms page, Delete popup opened</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">1. Click </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>...</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> -&gt; Select "Xóa" (Delete).</t>
+    </r>
+  </si>
+  <si>
+    <t>1. Click the "ĐÓNG" (Close) button.</t>
+  </si>
+  <si>
+    <t>1. Attempt to click and type into the "Mã*" field.</t>
+  </si>
+  <si>
+    <t>1. Observe the "Hình ảnh" section.</t>
+  </si>
+  <si>
+    <t>1. Click the "Trạng thái" dropdown.
+2. Select a different status (e.g., change to "Không hoạt động").
+3. Click "LƯU".</t>
+  </si>
+  <si>
+    <t>1. Click the x icon inside the "Trạng thái" dropdown box to clear the selection.
+2. Click "LƯU".</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
+  </si>
+  <si>
+    <t>System should prevent saving and require a Status to be selected, showing a validation error.</t>
+  </si>
+  <si>
+    <t>The dropdown allows selection, and the new status is saved and updated on the list page.</t>
+  </si>
+  <si>
+    <t>The current image of the room should be displayed correctly.</t>
+  </si>
+  <si>
+    <t>The field should be disabled (greyed out) and prevent any text input.</t>
+  </si>
+  <si>
+    <t>The field is fully editable.</t>
+  </si>
+  <si>
+    <t>Broken image icon is shown.</t>
+  </si>
+  <si>
+    <t>Fail</t>
+  </si>
+  <si>
+    <t>The popup closes, no data is deleted, and user remains on the Rooms list page.</t>
+  </si>
+  <si>
+    <t>System displays a confirmation popup showing the exact Room Code (e.g., "Bạn có chắc muốn xóa PH010") with "ĐÓNG" and "XÓA" buttons.</t>
+  </si>
+  <si>
+    <t>students</t>
+  </si>
+  <si>
+    <t>Verify UI of Student list page</t>
+  </si>
+  <si>
+    <t>Logged into YoEdu, on Students page</t>
+  </si>
+  <si>
+    <t>1. Observe the data table header and action buttons.</t>
+  </si>
+  <si>
+    <t>Table displays STT, Mã, Tên, Khối lớp, Tên PH, SDT PH, Người giới thiệu, Trạng thái, Tác vụ. Top buttons (Filter, Add, Refresh, Export) are visible.</t>
+  </si>
+  <si>
+    <t>Verify Search functionality by Student Code/Name</t>
+  </si>
+  <si>
+    <t>Verify Advanced Filter toggle (Funnel icon)</t>
+  </si>
+  <si>
+    <t>Verify "Trạng thái" (Status) column filter</t>
+  </si>
+  <si>
+    <t>Verify Refresh list button</t>
+  </si>
+  <si>
+    <t>Verify Export to Excel functionality</t>
+  </si>
+  <si>
+    <t>1. Click the Export Excel icon.</t>
+  </si>
+  <si>
+    <t>On Students page</t>
+  </si>
+  <si>
+    <t>1. Click the Refresh icon (circular arrows).</t>
+  </si>
+  <si>
+    <t>1. Click the small dropdown arrow next to the "Trạng thái" column header.
+2. Select a status (e.g., Active).</t>
+  </si>
+  <si>
+    <t>1. Click the Filter (Funnel) icon next to the Search box.</t>
+  </si>
+  <si>
+    <t>1. Enter "HV2050" or "dytrue" in the Search box.
+2. Press Enter.</t>
+  </si>
+  <si>
+    <t>Verify Parent Phone Number (SDT PH) is masked for privacy</t>
+  </si>
+  <si>
+    <t>Verify hyperlink navigation to Student Details</t>
+  </si>
+  <si>
+    <t>Verify Pagination functionality with large datasets</t>
+  </si>
+  <si>
+    <t>1. Observe the "SDT PH" column for any student.</t>
+  </si>
+  <si>
+    <t>1. Click the blue link in "Mã Học Viên" or "Tên Học Viên" (e.g., HV2055).</t>
+  </si>
+  <si>
+    <t>1. Scroll down to pagination.
+2. Click on the last page number (e.g., 55) or 'Next' icon.</t>
+  </si>
+  <si>
+    <t>System successfully loads the last page of students without performance lag.</t>
+  </si>
+  <si>
+    <t>System navigates to the Read-only Details page for that student.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">The phone numbers are partially masked with asterisks (e.g., </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>0891***456</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>) to protect personal data.</t>
+    </r>
+  </si>
+  <si>
+    <t>Table reloads and displays only the matching student(s).</t>
+  </si>
+  <si>
+    <t>An advanced filtering panel or modal expands, allowing users to filter by specific criteria (e.g., Grade, Status).</t>
+  </si>
+  <si>
+    <t>The data table filters and shows only students with the selected status.</t>
+  </si>
+  <si>
+    <t>The data table reloads without refreshing the entire web browser page.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">A </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>.xlsx</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> or </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>.csv</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> file containing the student list is successfully downloaded to the computer.</t>
+    </r>
+  </si>
+  <si>
+    <t>Verify Export Excel applies currently filtered data</t>
+  </si>
+  <si>
+    <t>On Students page with an active filter or search query applied</t>
+  </si>
+  <si>
+    <t>1. Filter the list (e.g., search for "con").
+2. Click the Export Excel icon.
+3. Open the downloaded file.</t>
+  </si>
+  <si>
+    <t>The exported Excel file must ONLY contain the filtered rows currently visible, NOT the entire database.</t>
+  </si>
+  <si>
+    <t>Verify Pagination boundary on the final page</t>
+  </si>
+  <si>
+    <t>1. Click on the last page number (Page 55).
+2. Observe the 'Next' arrow &gt; button.</t>
+  </si>
+  <si>
+    <t>The 'Next' arrow button should become disabled or unclickable since user is on the final page.</t>
+  </si>
+  <si>
+    <t>Verify Advanced Search popup UI</t>
+  </si>
+  <si>
+    <t>Verify successful search by valid Referrer</t>
+  </si>
+  <si>
+    <t>Verify search with non-existent Referrer</t>
+  </si>
+  <si>
+    <t>Verify "HỦY" (Cancel) button functionality</t>
+  </si>
+  <si>
+    <t>Verify "XÓA BỘ LỌC" (Clear Filter) functionality</t>
+  </si>
+  <si>
+    <t>On Students page with an active Referrer search applied</t>
+  </si>
+  <si>
+    <t>On Students page, Advanced Search opened</t>
+  </si>
+  <si>
+    <t>1. Click the Filter (Funnel) icon.</t>
+  </si>
+  <si>
+    <t>"TÌM KIẾM NÂNG CAO" popup opens containing an input field for referrer, and 3 buttons: "XÓA BỘ LỌC", "HỦY", "TÌM KIẾM".</t>
+  </si>
+  <si>
+    <t>1. Enter an existing Referrer name in the text box.
+2. Click "TÌM KIẾM".</t>
+  </si>
+  <si>
+    <t>The popup closes and the data table updates to display ONLY the students associated with that referrer.</t>
+  </si>
+  <si>
+    <t>1. Enter a non-existent name (e.g., "XYZ_NoName").
+2. Click "TÌM KIẾM".</t>
+  </si>
+  <si>
+    <t>1. Enter any text into the text box.
+2. Click the "HỦY" button.</t>
+  </si>
+  <si>
+    <t>1. Click the Filter (Funnel) icon to reopen the popup.
+2. Click "XÓA BỘ LỌC".</t>
+  </si>
+  <si>
+    <t>The popup closes. The filter is removed, and the data table resets to display the default full list of all students.</t>
+  </si>
+  <si>
+    <t>The popup closes. The entered text is NOT applied to the table, and the list remains unchanged.</t>
+  </si>
+  <si>
+    <t>The table reloads and displays a "No data found" or empty state message.</t>
+  </si>
+  <si>
+    <t>Verify "Tải lại trang" retains active search and filter states</t>
+  </si>
+  <si>
+    <t>1. Enter a search term in the global search box.
+2. Apply a filter using the Advanced Search popup.
+3. Click the "Tải lại trang" (Refresh) icon.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">The table reloads fetching new data, but </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>retains</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> the entered search term and active filters.</t>
+    </r>
+  </si>
+  <si>
+    <t>The button clears all search terms and filters, resetting the table to the default initial state.</t>
+  </si>
+  <si>
+    <t>Verify Action menu options</t>
+  </si>
+  <si>
+    <t>Verify "Đăng ký" navigation</t>
+  </si>
+  <si>
+    <t>Verify "Nộp học phí" navigation</t>
+  </si>
+  <si>
+    <t>Verify "Quá trình học" navigation</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">1. Click </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>...</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> on a student.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">1. Click </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>...</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> -&gt; Select "Đăng ký".</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">1. Click </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>...</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> -&gt; Select "Nộp học phí".</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">1. Click </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>...</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> -&gt; Select "Quá trình học".</t>
+    </r>
+  </si>
+  <si>
+    <t>System navigates to the academic history/progress page of that student.</t>
+  </si>
+  <si>
+    <t>System navigates to the payment/invoice page for that specific student.</t>
+  </si>
+  <si>
+    <t>System navigates to a course/class registration page for that specific student.</t>
+  </si>
+  <si>
+    <t>Menu displays: Xem, Sửa, Xóa, Đăng ký, Nộp học phí, Quá trình học.</t>
+  </si>
+  <si>
+    <t>Verify creation using "LƯU" button</t>
+  </si>
+  <si>
+    <t>Verify creation using "LƯU VÀ ĐĂNG KÝ"</t>
+  </si>
+  <si>
+    <t>Verify auto-generation of Student Code (Mã học viên)</t>
+  </si>
+  <si>
+    <t>Verify default password assignment</t>
+  </si>
+  <si>
+    <t>On "Tạo mới học viên" page</t>
+  </si>
+  <si>
+    <t>1. Fill all required fields (*).
+2. Click "LƯU".</t>
+  </si>
+  <si>
+    <t>1. Fill all required fields (*).
+2. Click "LƯU VÀ ĐĂNG KÝ".</t>
+  </si>
+  <si>
+    <t>1. Fill required fields but leave "Mã học viên *" BLANK.
+2. Click "LƯU".</t>
+  </si>
+  <si>
+    <t>1. Leave "Mật khẩu" blank.
+2. Fill other required fields and Save.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">System sets the student's password to </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>123456</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> by default. </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(Can be verified by logging in as that student later or checking DB)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <t>System successfully creates the student and automatically assigns a unique Student Code (as stated in the UI note).</t>
+  </si>
+  <si>
+    <t>Data saves, system immediately redirects to the "Đăng ký" (Course Registration) page for this new student.</t>
+  </si>
+  <si>
+    <t>Data saves successfully, system redirects to the Student list page.</t>
+  </si>
+  <si>
+    <t>Verify validation for all required fields</t>
+  </si>
+  <si>
+    <t>Verify Parent Name field restricts numeric input</t>
+  </si>
+  <si>
+    <t>Verify Phone Number format validation</t>
+  </si>
+  <si>
+    <t>Verify Email format validation</t>
+  </si>
+  <si>
+    <t>Verify Date of Birth (Ngày sinh) format &amp; logic</t>
+  </si>
+  <si>
+    <t>Verify Password visibility toggle</t>
+  </si>
+  <si>
+    <t>1. Leave ALL fields blank.
+2. Click "LƯU".</t>
+  </si>
+  <si>
+    <t>1. Enter numbers (e.g., 123333) in "Tên phụ huynh".
+2. Fill other fields and Save.</t>
+  </si>
+  <si>
+    <t>1. Enter letters/special characters (e.g., abc@#) in "Số điện thoại phụ huynh".
+2. Save.</t>
+  </si>
+  <si>
+    <t>1. Enter an invalid email (e.g., testemail.com missing @).
+2. Save.</t>
+  </si>
+  <si>
+    <t>1. Enter a future date (e.g., 01/01/2030) OR invalid format.
+2. Save.</t>
+  </si>
+  <si>
+    <t>1. Type abcd in "Mật khẩu".
+2. Click the eye icon next to the field.</t>
+  </si>
+  <si>
+    <r>
+      <t>The password text changes from masked dots (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>••••</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>) to plain text (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>abcd</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>) and vice versa.</t>
+    </r>
+  </si>
+  <si>
+    <t>System shows validation error (e.g., "Ngày sinh không được lớn hơn hiện tại").</t>
+  </si>
+  <si>
+    <t>System shows validation error: "Email không hợp lệ" (Invalid email format).</t>
+  </si>
+  <si>
+    <t>System shows validation error: "Số điện thoại không hợp lệ" (Invalid phone number).</t>
+  </si>
+  <si>
+    <t>System should show an error "Tên không hợp lệ" (Invalid name) and prevent saving.</t>
+  </si>
+  <si>
+    <r>
+      <t>System prevents saving and highlights missing required fields (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>Số điện thoại phụ huynh</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>Tên phụ huynh</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>Tên học viên</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>Ngày sinh</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>Giới tính</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>).</t>
+    </r>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="4">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial Unicode MS"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -76,7 +1318,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -84,14 +1326,39 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -372,11 +1639,22 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I1"/>
-  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9C1FC02D-0E6B-49D9-B5E0-C8FE485D63FD}">
+  <dimension ref="A1:I45"/>
+  <sheetFormatPr defaultRowHeight="14.75"/>
+  <cols>
+    <col min="1" max="1" width="8.31640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="54.81640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="32.31640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="67.953125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="95.26953125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="96.5" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="5.7265625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="5.453125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.75">
+    <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -403,6 +1681,970 @@
       </c>
       <c r="I1" s="1" t="s">
         <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" ht="29.5">
+      <c r="A2" s="1">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I2" s="1"/>
+    </row>
+    <row r="3" spans="1:9" ht="29.5">
+      <c r="A3" s="1">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I3" s="1"/>
+    </row>
+    <row r="4" spans="1:9" ht="44.25">
+      <c r="A4" s="1">
+        <v>3</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="G4" s="1"/>
+      <c r="H4" s="1"/>
+      <c r="I4" s="1"/>
+    </row>
+    <row r="5" spans="1:9">
+      <c r="A5" s="1">
+        <v>4</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="G5" s="1"/>
+      <c r="H5" s="1"/>
+      <c r="I5" s="1"/>
+    </row>
+    <row r="6" spans="1:9" ht="29.5">
+      <c r="A6" s="1">
+        <v>5</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="G6" s="1"/>
+      <c r="H6" s="1"/>
+      <c r="I6" s="1"/>
+    </row>
+    <row r="7" spans="1:9">
+      <c r="A7" s="1">
+        <v>6</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="G7" s="1"/>
+      <c r="H7" s="1"/>
+      <c r="I7" s="1"/>
+    </row>
+    <row r="8" spans="1:9">
+      <c r="A8" s="1">
+        <v>7</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="G8" s="1"/>
+      <c r="H8" s="1"/>
+      <c r="I8" s="1"/>
+    </row>
+    <row r="9" spans="1:9" ht="44.25">
+      <c r="A9" s="1">
+        <v>8</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="G9" s="1"/>
+      <c r="H9" s="1"/>
+      <c r="I9" s="1"/>
+    </row>
+    <row r="10" spans="1:9" ht="29.5">
+      <c r="A10" s="1">
+        <v>9</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="G10" s="1"/>
+      <c r="H10" s="1"/>
+      <c r="I10" s="1"/>
+    </row>
+    <row r="11" spans="1:9" ht="44.25">
+      <c r="A11" s="1">
+        <v>10</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="G11" s="1"/>
+      <c r="H11" s="1"/>
+      <c r="I11" s="1"/>
+    </row>
+    <row r="12" spans="1:9">
+      <c r="A12" s="1">
+        <v>11</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="G12" s="1"/>
+      <c r="H12" s="1"/>
+      <c r="I12" s="1"/>
+    </row>
+    <row r="13" spans="1:9" ht="29.5">
+      <c r="A13" s="1">
+        <v>12</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="G13" s="1"/>
+      <c r="H13" s="1"/>
+      <c r="I13" s="1"/>
+    </row>
+    <row r="14" spans="1:9" ht="29.5">
+      <c r="A14" s="1">
+        <v>13</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="G14" s="1"/>
+      <c r="H14" s="1"/>
+      <c r="I14" s="1"/>
+    </row>
+    <row r="15" spans="1:9" ht="29.5">
+      <c r="A15" s="1">
+        <v>14</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="G15" s="1"/>
+      <c r="H15" s="1"/>
+      <c r="I15" s="1"/>
+    </row>
+    <row r="16" spans="1:9" ht="44.25">
+      <c r="A16" s="1">
+        <v>15</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="G16" s="1"/>
+      <c r="H16" s="1"/>
+      <c r="I16" s="1"/>
+    </row>
+    <row r="17" spans="1:9">
+      <c r="A17" s="1">
+        <v>16</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="F17" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="G17" s="1"/>
+      <c r="H17" s="1"/>
+      <c r="I17" s="1"/>
+    </row>
+    <row r="18" spans="1:9" ht="29.5">
+      <c r="A18" s="1">
+        <v>17</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="G18" s="1"/>
+      <c r="H18" s="1"/>
+      <c r="I18" s="1"/>
+    </row>
+    <row r="19" spans="1:9" ht="29.5">
+      <c r="A19" s="1">
+        <v>18</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="F19" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="G19" s="1"/>
+      <c r="H19" s="1"/>
+      <c r="I19" s="1"/>
+    </row>
+    <row r="20" spans="1:9">
+      <c r="A20" s="1">
+        <v>19</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="F20" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="G20" s="1"/>
+      <c r="H20" s="1"/>
+      <c r="I20" s="1"/>
+    </row>
+    <row r="21" spans="1:9">
+      <c r="A21" s="1">
+        <v>20</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="F21" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="G21" s="1"/>
+      <c r="H21" s="1"/>
+      <c r="I21" s="1"/>
+    </row>
+    <row r="22" spans="1:9" ht="44.25">
+      <c r="A22" s="1">
+        <v>21</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="F22" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="G22" s="1"/>
+      <c r="H22" s="1"/>
+      <c r="I22" s="1"/>
+    </row>
+    <row r="23" spans="1:9" ht="44.25">
+      <c r="A23" s="1">
+        <v>22</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="F23" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="G23" s="1"/>
+      <c r="H23" s="1"/>
+      <c r="I23" s="1"/>
+    </row>
+    <row r="24" spans="1:9" ht="29.5">
+      <c r="A24" s="1">
+        <v>23</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="F24" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="G24" s="1"/>
+      <c r="H24" s="1"/>
+      <c r="I24" s="1"/>
+    </row>
+    <row r="25" spans="1:9" ht="29.5">
+      <c r="A25" s="1">
+        <v>24</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="F25" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="G25" s="1"/>
+      <c r="H25" s="1"/>
+      <c r="I25" s="1"/>
+    </row>
+    <row r="26" spans="1:9" ht="73.75">
+      <c r="A26" s="1">
+        <v>25</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="F26" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="G26" s="1"/>
+      <c r="H26" s="1"/>
+      <c r="I26" s="1"/>
+    </row>
+    <row r="27" spans="1:9" ht="29.5">
+      <c r="A27" s="1">
+        <v>26</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="F27" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="G27" s="1"/>
+      <c r="H27" s="1"/>
+      <c r="I27" s="1"/>
+    </row>
+    <row r="28" spans="1:9" ht="44.25">
+      <c r="A28" s="1">
+        <v>27</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="F28" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="G28" s="1"/>
+      <c r="H28" s="1"/>
+      <c r="I28" s="1"/>
+    </row>
+    <row r="29" spans="1:9" ht="29.5">
+      <c r="A29" s="1">
+        <v>28</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="F29" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="G29" s="1"/>
+      <c r="H29" s="1"/>
+      <c r="I29" s="1"/>
+    </row>
+    <row r="30" spans="1:9">
+      <c r="A30" s="1">
+        <v>29</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="E30" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="F30" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="G30" s="1"/>
+      <c r="H30" s="1"/>
+      <c r="I30" s="1"/>
+    </row>
+    <row r="31" spans="1:9" ht="29.5">
+      <c r="A31" s="1">
+        <v>30</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="F31" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="G31" s="1"/>
+      <c r="H31" s="1"/>
+      <c r="I31" s="1"/>
+    </row>
+    <row r="32" spans="1:9" ht="29.5">
+      <c r="A32" s="1">
+        <v>31</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="D32" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="F32" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="G32" s="1"/>
+      <c r="H32" s="1"/>
+      <c r="I32" s="1"/>
+    </row>
+    <row r="33" spans="1:9" ht="29.5">
+      <c r="A33" s="1">
+        <v>32</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="D33" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="F33" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="G33" s="1"/>
+      <c r="H33" s="1"/>
+      <c r="I33" s="1"/>
+    </row>
+    <row r="34" spans="1:9" ht="44.25">
+      <c r="A34" s="1">
+        <v>33</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="D34" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="E34" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="F34" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="G34" s="1"/>
+      <c r="H34" s="1"/>
+      <c r="I34" s="1"/>
+    </row>
+    <row r="35" spans="1:9" ht="29.5">
+      <c r="A35" s="1">
+        <v>34</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="D35" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="E35" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="F35" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="G35" s="1"/>
+      <c r="H35" s="1"/>
+      <c r="I35" s="1"/>
+    </row>
+    <row r="36" spans="1:9" ht="29.5">
+      <c r="A36" s="1">
+        <v>35</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="D36" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="E36" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="F36" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="G36" s="1"/>
+      <c r="H36" s="1"/>
+      <c r="I36" s="1"/>
+    </row>
+    <row r="37" spans="1:9">
+      <c r="A37" s="1">
+        <v>36</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="D37" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E37" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="F37" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="G37" s="1"/>
+      <c r="H37" s="1"/>
+      <c r="I37" s="1"/>
+    </row>
+    <row r="38" spans="1:9">
+      <c r="A38" s="1">
+        <v>37</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="D38" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="E38" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="F38" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="G38" s="1"/>
+      <c r="H38" s="1"/>
+      <c r="I38" s="1"/>
+    </row>
+    <row r="39" spans="1:9">
+      <c r="A39" s="1">
+        <v>38</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="D39" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="E39" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="F39" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="G39" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="H39" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="I39" s="1"/>
+    </row>
+    <row r="40" spans="1:9">
+      <c r="A40" s="1">
+        <v>39</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="D40" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="E40" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="F40" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="G40" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="H40" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="I40" s="1"/>
+    </row>
+    <row r="41" spans="1:9" ht="44.25">
+      <c r="A41" s="1">
+        <v>40</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="D41" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="E41" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="F41" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="G41" s="1"/>
+      <c r="H41" s="1"/>
+      <c r="I41" s="1"/>
+    </row>
+    <row r="42" spans="1:9" ht="29.5">
+      <c r="A42" s="1">
+        <v>41</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="D42" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="E42" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="F42" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="G42" s="1"/>
+      <c r="H42" s="1"/>
+      <c r="I42" s="1"/>
+    </row>
+    <row r="45" spans="1:9">
+      <c r="E45" t="s">
+        <v>134</v>
       </c>
     </row>
   </sheetData>
@@ -411,49 +2653,766 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9C1FC02D-0E6B-49D9-B5E0-C8FE485D63FD}">
-  <dimension ref="A1:I1"/>
-  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:I32"/>
+  <sheetFormatPr defaultRowHeight="14.75"/>
   <cols>
     <col min="1" max="1" width="8.31640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="7" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="4.2265625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.453125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="5.08984375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.6796875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.31640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7.7265625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="49.40625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="51.2265625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="59.1796875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="117.76953125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="75.04296875" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="5.7265625" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="5.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.75">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:9">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="3" t="s">
         <v>8</v>
       </c>
+    </row>
+    <row r="2" spans="1:9">
+      <c r="A2" s="4">
+        <v>1</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="G2" s="4"/>
+      <c r="H2" s="4"/>
+      <c r="I2" s="4"/>
+    </row>
+    <row r="3" spans="1:9" ht="29.5">
+      <c r="A3" s="4">
+        <v>2</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>159</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>169</v>
+      </c>
+      <c r="G3" s="4"/>
+      <c r="H3" s="4"/>
+      <c r="I3" s="4"/>
+    </row>
+    <row r="4" spans="1:9">
+      <c r="A4" s="4">
+        <v>3</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>170</v>
+      </c>
+      <c r="G4" s="4"/>
+      <c r="H4" s="4"/>
+      <c r="I4" s="4"/>
+    </row>
+    <row r="5" spans="1:9" ht="44.25">
+      <c r="A5" s="4">
+        <v>4</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>157</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="G5" s="4"/>
+      <c r="H5" s="4"/>
+      <c r="I5" s="4"/>
+    </row>
+    <row r="6" spans="1:9">
+      <c r="A6" s="4">
+        <v>5</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>172</v>
+      </c>
+      <c r="G6" s="4"/>
+      <c r="H6" s="4"/>
+      <c r="I6" s="4"/>
+    </row>
+    <row r="7" spans="1:9">
+      <c r="A7" s="4">
+        <v>6</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>154</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>173</v>
+      </c>
+      <c r="G7" s="4"/>
+      <c r="H7" s="4"/>
+      <c r="I7" s="4"/>
+    </row>
+    <row r="8" spans="1:9">
+      <c r="A8" s="4">
+        <v>7</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="G8" s="4"/>
+      <c r="H8" s="4"/>
+      <c r="I8" s="4"/>
+    </row>
+    <row r="9" spans="1:9">
+      <c r="A9" s="4">
+        <v>8</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>164</v>
+      </c>
+      <c r="F9" s="4" t="s">
+        <v>167</v>
+      </c>
+      <c r="G9" s="4"/>
+      <c r="H9" s="4"/>
+      <c r="I9" s="4"/>
+    </row>
+    <row r="10" spans="1:9" ht="29.5">
+      <c r="A10" s="4">
+        <v>9</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="E10" s="5" t="s">
+        <v>165</v>
+      </c>
+      <c r="F10" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="G10" s="4"/>
+      <c r="H10" s="4"/>
+      <c r="I10" s="4"/>
+    </row>
+    <row r="11" spans="1:9" ht="44.25">
+      <c r="A11" s="4">
+        <v>10</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>174</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>175</v>
+      </c>
+      <c r="E11" s="5" t="s">
+        <v>176</v>
+      </c>
+      <c r="F11" s="4" t="s">
+        <v>177</v>
+      </c>
+      <c r="G11" s="4"/>
+      <c r="H11" s="4"/>
+      <c r="I11" s="4"/>
+    </row>
+    <row r="12" spans="1:9" ht="29.5">
+      <c r="A12" s="4">
+        <v>11</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>178</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="E12" s="5" t="s">
+        <v>179</v>
+      </c>
+      <c r="F12" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="G12" s="4"/>
+      <c r="H12" s="4"/>
+      <c r="I12" s="4"/>
+    </row>
+    <row r="13" spans="1:9">
+      <c r="A13" s="4">
+        <v>12</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>181</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="E13" s="4" t="s">
+        <v>188</v>
+      </c>
+      <c r="F13" s="4" t="s">
+        <v>189</v>
+      </c>
+      <c r="G13" s="4"/>
+      <c r="H13" s="4"/>
+      <c r="I13" s="4"/>
+    </row>
+    <row r="14" spans="1:9" ht="29.5">
+      <c r="A14" s="4">
+        <v>13</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>182</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="E14" s="5" t="s">
+        <v>190</v>
+      </c>
+      <c r="F14" s="4" t="s">
+        <v>191</v>
+      </c>
+      <c r="G14" s="4"/>
+      <c r="H14" s="4"/>
+      <c r="I14" s="4"/>
+    </row>
+    <row r="15" spans="1:9" ht="29.5">
+      <c r="A15" s="4">
+        <v>14</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>183</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="E15" s="5" t="s">
+        <v>192</v>
+      </c>
+      <c r="F15" s="4" t="s">
+        <v>197</v>
+      </c>
+      <c r="G15" s="4"/>
+      <c r="H15" s="4"/>
+      <c r="I15" s="4"/>
+    </row>
+    <row r="16" spans="1:9" ht="29.5">
+      <c r="A16" s="4">
+        <v>15</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>184</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="E16" s="5" t="s">
+        <v>193</v>
+      </c>
+      <c r="F16" s="4" t="s">
+        <v>196</v>
+      </c>
+      <c r="G16" s="4"/>
+      <c r="H16" s="4"/>
+      <c r="I16" s="4"/>
+    </row>
+    <row r="17" spans="1:9" ht="29.5">
+      <c r="A17" s="4">
+        <v>16</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>185</v>
+      </c>
+      <c r="D17" s="4" t="s">
+        <v>186</v>
+      </c>
+      <c r="E17" s="5" t="s">
+        <v>194</v>
+      </c>
+      <c r="F17" s="4" t="s">
+        <v>195</v>
+      </c>
+      <c r="G17" s="4"/>
+      <c r="H17" s="4"/>
+      <c r="I17" s="4"/>
+    </row>
+    <row r="18" spans="1:9" ht="44.25">
+      <c r="A18" s="4">
+        <v>17</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>198</v>
+      </c>
+      <c r="D18" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="E18" s="5" t="s">
+        <v>199</v>
+      </c>
+      <c r="F18" s="4" t="s">
+        <v>200</v>
+      </c>
+      <c r="G18" s="4" t="s">
+        <v>201</v>
+      </c>
+      <c r="H18" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="I18" s="4"/>
+    </row>
+    <row r="19" spans="1:9">
+      <c r="A19" s="4">
+        <v>18</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>202</v>
+      </c>
+      <c r="D19" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="E19" s="4" t="s">
+        <v>206</v>
+      </c>
+      <c r="F19" s="4" t="s">
+        <v>213</v>
+      </c>
+      <c r="G19" s="4"/>
+      <c r="H19" s="4"/>
+      <c r="I19" s="4"/>
+    </row>
+    <row r="20" spans="1:9">
+      <c r="A20" s="4">
+        <v>19</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>203</v>
+      </c>
+      <c r="D20" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="E20" s="4" t="s">
+        <v>207</v>
+      </c>
+      <c r="F20" s="4" t="s">
+        <v>212</v>
+      </c>
+      <c r="G20" s="4"/>
+      <c r="H20" s="4"/>
+      <c r="I20" s="4"/>
+    </row>
+    <row r="21" spans="1:9">
+      <c r="A21" s="4">
+        <v>20</v>
+      </c>
+      <c r="B21" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="C21" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="D21" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="E21" s="4" t="s">
+        <v>208</v>
+      </c>
+      <c r="F21" s="4" t="s">
+        <v>211</v>
+      </c>
+      <c r="G21" s="4"/>
+      <c r="H21" s="4"/>
+      <c r="I21" s="4"/>
+    </row>
+    <row r="22" spans="1:9">
+      <c r="A22" s="4">
+        <v>21</v>
+      </c>
+      <c r="B22" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>205</v>
+      </c>
+      <c r="D22" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="E22" s="4" t="s">
+        <v>209</v>
+      </c>
+      <c r="F22" s="4" t="s">
+        <v>210</v>
+      </c>
+      <c r="G22" s="4"/>
+      <c r="H22" s="4"/>
+      <c r="I22" s="4"/>
+    </row>
+    <row r="23" spans="1:9" ht="29.5">
+      <c r="A23" s="4">
+        <v>22</v>
+      </c>
+      <c r="B23" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="C23" s="4" t="s">
+        <v>214</v>
+      </c>
+      <c r="D23" s="4" t="s">
+        <v>218</v>
+      </c>
+      <c r="E23" s="5" t="s">
+        <v>219</v>
+      </c>
+      <c r="F23" s="4" t="s">
+        <v>226</v>
+      </c>
+      <c r="G23" s="4"/>
+      <c r="H23" s="4"/>
+      <c r="I23" s="4"/>
+    </row>
+    <row r="24" spans="1:9" ht="29.5">
+      <c r="A24" s="4">
+        <v>23</v>
+      </c>
+      <c r="B24" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="C24" s="4" t="s">
+        <v>215</v>
+      </c>
+      <c r="D24" s="4" t="s">
+        <v>218</v>
+      </c>
+      <c r="E24" s="5" t="s">
+        <v>220</v>
+      </c>
+      <c r="F24" s="4" t="s">
+        <v>225</v>
+      </c>
+      <c r="G24" s="4"/>
+      <c r="H24" s="4"/>
+      <c r="I24" s="4"/>
+    </row>
+    <row r="25" spans="1:9" ht="29.5">
+      <c r="A25" s="4">
+        <v>24</v>
+      </c>
+      <c r="B25" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="C25" s="4" t="s">
+        <v>216</v>
+      </c>
+      <c r="D25" s="4" t="s">
+        <v>218</v>
+      </c>
+      <c r="E25" s="5" t="s">
+        <v>221</v>
+      </c>
+      <c r="F25" s="4" t="s">
+        <v>224</v>
+      </c>
+      <c r="G25" s="4"/>
+      <c r="H25" s="4"/>
+      <c r="I25" s="4"/>
+    </row>
+    <row r="26" spans="1:9" ht="29.5">
+      <c r="A26" s="4">
+        <v>25</v>
+      </c>
+      <c r="B26" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="C26" s="4" t="s">
+        <v>217</v>
+      </c>
+      <c r="D26" s="4" t="s">
+        <v>218</v>
+      </c>
+      <c r="E26" s="5" t="s">
+        <v>222</v>
+      </c>
+      <c r="F26" s="4" t="s">
+        <v>223</v>
+      </c>
+      <c r="G26" s="4"/>
+      <c r="H26" s="4"/>
+      <c r="I26" s="4"/>
+    </row>
+    <row r="27" spans="1:9" ht="29.5">
+      <c r="A27" s="4">
+        <v>26</v>
+      </c>
+      <c r="B27" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="C27" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="D27" s="4" t="s">
+        <v>218</v>
+      </c>
+      <c r="E27" s="5" t="s">
+        <v>233</v>
+      </c>
+      <c r="F27" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="G27" s="4"/>
+      <c r="H27" s="4"/>
+      <c r="I27" s="4"/>
+    </row>
+    <row r="28" spans="1:9" ht="29.5">
+      <c r="A28" s="4">
+        <v>27</v>
+      </c>
+      <c r="B28" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="C28" s="4" t="s">
+        <v>228</v>
+      </c>
+      <c r="D28" s="4" t="s">
+        <v>218</v>
+      </c>
+      <c r="E28" s="5" t="s">
+        <v>234</v>
+      </c>
+      <c r="F28" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="G28" s="4"/>
+      <c r="H28" s="4"/>
+      <c r="I28" s="4"/>
+    </row>
+    <row r="29" spans="1:9" ht="44.25">
+      <c r="A29" s="4">
+        <v>28</v>
+      </c>
+      <c r="B29" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="C29" s="4" t="s">
+        <v>229</v>
+      </c>
+      <c r="D29" s="4" t="s">
+        <v>218</v>
+      </c>
+      <c r="E29" s="5" t="s">
+        <v>235</v>
+      </c>
+      <c r="F29" s="4" t="s">
+        <v>242</v>
+      </c>
+      <c r="G29" s="4"/>
+      <c r="H29" s="4"/>
+      <c r="I29" s="4"/>
+    </row>
+    <row r="30" spans="1:9" ht="29.5">
+      <c r="A30" s="4">
+        <v>29</v>
+      </c>
+      <c r="B30" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="C30" s="4" t="s">
+        <v>230</v>
+      </c>
+      <c r="D30" s="4" t="s">
+        <v>218</v>
+      </c>
+      <c r="E30" s="5" t="s">
+        <v>236</v>
+      </c>
+      <c r="F30" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="G30" s="4"/>
+      <c r="H30" s="4"/>
+      <c r="I30" s="4"/>
+    </row>
+    <row r="31" spans="1:9" ht="29.5">
+      <c r="A31" s="4">
+        <v>30</v>
+      </c>
+      <c r="B31" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="C31" s="4" t="s">
+        <v>231</v>
+      </c>
+      <c r="D31" s="4" t="s">
+        <v>218</v>
+      </c>
+      <c r="E31" s="5" t="s">
+        <v>237</v>
+      </c>
+      <c r="F31" s="4" t="s">
+        <v>240</v>
+      </c>
+      <c r="G31" s="4"/>
+      <c r="H31" s="4"/>
+      <c r="I31" s="4"/>
+    </row>
+    <row r="32" spans="1:9" ht="29.5">
+      <c r="A32" s="4">
+        <v>31</v>
+      </c>
+      <c r="B32" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="C32" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="D32" s="4" t="s">
+        <v>218</v>
+      </c>
+      <c r="E32" s="5" t="s">
+        <v>238</v>
+      </c>
+      <c r="F32" s="4" t="s">
+        <v>239</v>
+      </c>
+      <c r="G32" s="4"/>
+      <c r="H32" s="4"/>
+      <c r="I32" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
